--- a/public/downloads/TMBill_Standardized_Reporting_Control_Pack.xlsx
+++ b/public/downloads/TMBill_Standardized_Reporting_Control_Pack.xlsx
@@ -2,32 +2,33 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rdafa65036fe34794"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="2" r:id="R5012c29f91f040a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Register" sheetId="3" r:id="R51b4e98938ed4305"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metric Dictionary" sheetId="4" r:id="R494ecd92065b4f4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canonical Data Model" sheetId="5" r:id="R57926e63cdee4063"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales Z Summary" sheetId="6" r:id="R0fc95652b5604de1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Audit" sheetId="7" r:id="Rc1abfd2c3df54375"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Order Type Summary" sheetId="8" r:id="R5108186e4f9e41fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payment Type Summary" sheetId="9" r:id="Rae6bf6174ed244d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discount Summary" sheetId="10" r:id="R99426b143752467f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expense Summary" sheetId="11" r:id="Reb59fcbc898740b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bill Summary" sheetId="12" r:id="R8fc9e5e177c54cfd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Delivery Boy Summary" sheetId="13" r:id="Rb63404ea271f4bf7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Waiter Summary" sheetId="14" r:id="R58a4f275df9c4bf4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product Group Summary" sheetId="15" r:id="R686be1c8816843f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kitchen Dept Summary" sheetId="16" r:id="Rb7c31bf3a13f44f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Category Summary" sheetId="17" r:id="Rced21494e50940ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sold Items Summary" sheetId="18" r:id="Rcc41453508864feb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cancel Items Summary" sheetId="19" r:id="Rd1077fe1a4ae40cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wallet Summary" sheetId="20" r:id="R0805ce501ad8475e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Due Received" sheetId="21" r:id="R41a8b048f3744e1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Due Receivable" sheetId="22" r:id="Ree5ce51c2f554550"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payment Variance" sheetId="23" r:id="Rf032d9b034644873"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Currency Denoms" sheetId="24" r:id="R2fe5168bce804047"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Order Source Summary" sheetId="25" r:id="R4fdfe6bbaebd4aef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build Rules" sheetId="26" r:id="R4b63edc739c540c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R294652b4bc9849af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="2" r:id="R29a90e0891704c56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Register" sheetId="3" r:id="Rc86edb5293784124"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metric Dictionary" sheetId="4" r:id="R525d12d5da7c448d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canonical Data Model" sheetId="5" r:id="Raf22e9a170344943"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales Z Summary" sheetId="6" r:id="R661e119ed59e4389"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Audit" sheetId="7" r:id="R2e87269843dd42c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Order Type Summary" sheetId="8" r:id="R7f472d54aa064e6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payment Type Summary" sheetId="9" r:id="R8e82edc951644526"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discount Summary" sheetId="10" r:id="R081b8aeaa8064938"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expense Summary" sheetId="11" r:id="R0bbaa8bfdfcc45d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bill Summary" sheetId="12" r:id="R80c4372496bc4885"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Delivery Boy Summary" sheetId="13" r:id="R4ea0ae9ab0bd4bfe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Waiter Summary" sheetId="14" r:id="Ra1b25241f45e4954"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product Group Summary" sheetId="15" r:id="Rac59af204fd544c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kitchen Dept Summary" sheetId="16" r:id="R42160aa9e1ad458a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Category Summary" sheetId="17" r:id="R871d25b6081b46b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sold Items Summary" sheetId="18" r:id="Raf4e86d8ec6a43b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cancel Items Summary" sheetId="19" r:id="Rde73db35a4c9478c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wallet Summary" sheetId="20" r:id="R9be4b008a1e749fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Due Received" sheetId="21" r:id="R50951ed2253b4463"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Due Receivable" sheetId="22" r:id="R0b633493eb0a43e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payment Variance" sheetId="23" r:id="Rc08f4dd0fc294297"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Currency Denoms" sheetId="24" r:id="R9c43384522314205"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Order Source Summary" sheetId="25" r:id="R734a5f9e53d54e0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build Rules" sheetId="26" r:id="Rf78a502095c645c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Channel Colour Legend" sheetId="27" r:id="Rb546bfcea96a4d20"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -41,7 +42,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="#,##0.00;[Red]-#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="6">
+  <x:fonts count="9">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -76,8 +77,26 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF211D00"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF063E3A"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF262100"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="22">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -102,6 +121,86 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF0F766E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF173D32"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF3668A9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF7B57A5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2F9470"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF58220"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFDB00"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF00CDBC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF36A853"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF7C3F98"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFD800"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF386C9B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF3F8A5D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF52677D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFA36B12"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFB43B35"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF68756F"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -201,7 +300,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="41">
+  <x:cellXfs count="90">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -284,6 +383,87 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -6686,6 +6866,281 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="35" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="46" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="42" t="str">
+        <x:v>Order Type &amp; Payment Colour Standard</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="44" t="str">
+        <x:v>Channel / tender</x:v>
+      </x:c>
+      <x:c r="B4" s="44" t="str">
+        <x:v>Role</x:v>
+      </x:c>
+      <x:c r="C4" s="44" t="str">
+        <x:v>Colour use</x:v>
+      </x:c>
+      <x:c r="D4" s="44" t="str">
+        <x:v>Control note</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="47" t="str">
+        <x:v>Dine In</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>Order type</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>Same colour in dashboard, Excel and PDF</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>Red exception styling always overrides a channel colour.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="50" t="str">
+        <x:v>Pickup</x:v>
+      </x:c>
+      <x:c r="B6" s="9" t="str">
+        <x:v>Order type</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="str">
+        <x:v>Same colour in dashboard, Excel and PDF</x:v>
+      </x:c>
+      <x:c r="D6" s="9" t="str">
+        <x:v>Red exception styling always overrides a channel colour.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="53" t="str">
+        <x:v>Delivery</x:v>
+      </x:c>
+      <x:c r="B7" s="9" t="str">
+        <x:v>Order type</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="str">
+        <x:v>Same colour in dashboard, Excel and PDF</x:v>
+      </x:c>
+      <x:c r="D7" s="9" t="str">
+        <x:v>Red exception styling always overrides a channel colour.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="56" t="str">
+        <x:v>Talabat</x:v>
+      </x:c>
+      <x:c r="B8" s="9" t="str">
+        <x:v>Order type</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="str">
+        <x:v>Same colour in dashboard, Excel and PDF</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="str">
+        <x:v>Red exception styling always overrides a channel colour.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="59" t="str">
+        <x:v>Noon Food</x:v>
+      </x:c>
+      <x:c r="B9" s="9" t="str">
+        <x:v>Order type</x:v>
+      </x:c>
+      <x:c r="C9" s="9" t="str">
+        <x:v>Same colour in dashboard, Excel and PDF</x:v>
+      </x:c>
+      <x:c r="D9" s="9" t="str">
+        <x:v>Red exception styling always overrides a channel colour.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="59" t="str">
+        <x:v>Noonfood</x:v>
+      </x:c>
+      <x:c r="B10" s="9" t="str">
+        <x:v>Order type</x:v>
+      </x:c>
+      <x:c r="C10" s="9" t="str">
+        <x:v>Same colour in dashboard, Excel and PDF</x:v>
+      </x:c>
+      <x:c r="D10" s="9" t="str">
+        <x:v>Red exception styling always overrides a channel colour.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="62" t="str">
+        <x:v>Deliveroo</x:v>
+      </x:c>
+      <x:c r="B11" s="9" t="str">
+        <x:v>Order type</x:v>
+      </x:c>
+      <x:c r="C11" s="9" t="str">
+        <x:v>Same colour in dashboard, Excel and PDF</x:v>
+      </x:c>
+      <x:c r="D11" s="9" t="str">
+        <x:v>Red exception styling always overrides a channel colour.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="65" t="str">
+        <x:v>Careem</x:v>
+      </x:c>
+      <x:c r="B12" s="9" t="str">
+        <x:v>Order type</x:v>
+      </x:c>
+      <x:c r="C12" s="9" t="str">
+        <x:v>Same colour in dashboard, Excel and PDF</x:v>
+      </x:c>
+      <x:c r="D12" s="9" t="str">
+        <x:v>Red exception styling always overrides a channel colour.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="68" t="str">
+        <x:v>Smiles</x:v>
+      </x:c>
+      <x:c r="B13" s="9" t="str">
+        <x:v>Order type</x:v>
+      </x:c>
+      <x:c r="C13" s="9" t="str">
+        <x:v>Same colour in dashboard, Excel and PDF</x:v>
+      </x:c>
+      <x:c r="D13" s="9" t="str">
+        <x:v>Red exception styling always overrides a channel colour.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="71" t="str">
+        <x:v>Keeta</x:v>
+      </x:c>
+      <x:c r="B14" s="9" t="str">
+        <x:v>Order type</x:v>
+      </x:c>
+      <x:c r="C14" s="9" t="str">
+        <x:v>Same colour in dashboard, Excel and PDF</x:v>
+      </x:c>
+      <x:c r="D14" s="9" t="str">
+        <x:v>Red exception styling always overrides a channel colour.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="74" t="str">
+        <x:v>Card</x:v>
+      </x:c>
+      <x:c r="B15" s="9" t="str">
+        <x:v>Payment type</x:v>
+      </x:c>
+      <x:c r="C15" s="9" t="str">
+        <x:v>Same colour in dashboard, Excel and PDF</x:v>
+      </x:c>
+      <x:c r="D15" s="9" t="str">
+        <x:v>Red exception styling always overrides a channel colour.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="77" t="str">
+        <x:v>Cash</x:v>
+      </x:c>
+      <x:c r="B16" s="9" t="str">
+        <x:v>Payment type</x:v>
+      </x:c>
+      <x:c r="C16" s="9" t="str">
+        <x:v>Same colour in dashboard, Excel and PDF</x:v>
+      </x:c>
+      <x:c r="D16" s="9" t="str">
+        <x:v>Red exception styling always overrides a channel colour.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="80" t="str">
+        <x:v>Card,Cash</x:v>
+      </x:c>
+      <x:c r="B17" s="9" t="str">
+        <x:v>Payment type</x:v>
+      </x:c>
+      <x:c r="C17" s="9" t="str">
+        <x:v>Same colour in dashboard, Excel and PDF</x:v>
+      </x:c>
+      <x:c r="D17" s="9" t="str">
+        <x:v>Red exception styling always overrides a channel colour.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="80" t="str">
+        <x:v>Split</x:v>
+      </x:c>
+      <x:c r="B18" s="9" t="str">
+        <x:v>Payment type</x:v>
+      </x:c>
+      <x:c r="C18" s="9" t="str">
+        <x:v>Same colour in dashboard, Excel and PDF</x:v>
+      </x:c>
+      <x:c r="D18" s="9" t="str">
+        <x:v>Red exception styling always overrides a channel colour.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="83" t="str">
+        <x:v>Wallet</x:v>
+      </x:c>
+      <x:c r="B19" s="9" t="str">
+        <x:v>Payment type</x:v>
+      </x:c>
+      <x:c r="C19" s="9" t="str">
+        <x:v>Same colour in dashboard, Excel and PDF</x:v>
+      </x:c>
+      <x:c r="D19" s="9" t="str">
+        <x:v>Red exception styling always overrides a channel colour.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="86" t="str">
+        <x:v>Due</x:v>
+      </x:c>
+      <x:c r="B20" s="9" t="str">
+        <x:v>Payment type</x:v>
+      </x:c>
+      <x:c r="C20" s="9" t="str">
+        <x:v>Same colour in dashboard, Excel and PDF</x:v>
+      </x:c>
+      <x:c r="D20" s="9" t="str">
+        <x:v>Red exception styling always overrides a channel colour.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="89" t="str">
+        <x:v>Unclassified</x:v>
+      </x:c>
+      <x:c r="B21" s="9" t="str">
+        <x:v>Payment type</x:v>
+      </x:c>
+      <x:c r="C21" s="9" t="str">
+        <x:v>Same colour in dashboard, Excel and PDF</x:v>
+      </x:c>
+      <x:c r="D21" s="9" t="str">
+        <x:v>Red exception styling always overrides a channel colour.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:D2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
